--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="47">
   <si>
     <t>Result</t>
   </si>
@@ -217,6 +217,54 @@
   </si>
   <si>
     <t>Fri Jan 02 19:46:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:27:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:28:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:28:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:29:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:31:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:32:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:33:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:34:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:36:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:38:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 13:39:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 15:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 15:10:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 15:24:38 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -599,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="12.90625" collapsed="true"/>
@@ -628,13 +676,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -657,11 +705,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -673,17 +721,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -745,7 +793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CD28ED-6B88-4076-A023-4B2AA175CC49}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="5.6328125" collapsed="true"/>
@@ -775,13 +823,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -804,11 +852,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
+      <c r="B2" t="s" s="0">
+        <v>32</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -820,17 +868,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -889,7 +937,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38E6C38-F14D-4B06-9F0D-017FEF3E0BF1}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="32.90625" collapsed="true"/>
@@ -917,13 +965,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -946,11 +994,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>26</v>
+      <c r="B2" t="s" s="0">
+        <v>46</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -962,17 +1010,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1031,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACB12DE-9459-4B21-A76D-74D1C2CFA77A}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.81640625" collapsed="true"/>
@@ -1059,13 +1107,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1088,11 +1136,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
+      <c r="B2" t="s" s="0">
+        <v>45</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1104,17 +1152,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">

--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="48">
   <si>
     <t>Result</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Mon Jul 06 15:24:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 21 19:12:53 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1143,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{F82A1362-39A1-42AC-8A8D-1391BF42EF43}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4231D5-926B-41FD-8272-D15A641E13A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CVCSPNoCFPS_RecMonthly" r:id="rId1" sheetId="1"/>
-    <sheet name="CVCSPNoCFCC_RecMonthly" r:id="rId2" sheetId="2"/>
-    <sheet name="CVCSPNoCFPC_RecMonthly" r:id="rId3" sheetId="3"/>
-    <sheet name="CVCSPNoCFCorp_RecMonthly" r:id="rId4" sheetId="4"/>
+    <sheet name="CVCSPNoCFPS_RecMonthly" sheetId="1" r:id="rId1"/>
+    <sheet name="CVCSPNoCFCC_RecMonthly" sheetId="2" r:id="rId2"/>
+    <sheet name="CVCSPNoCFPC_RecMonthly" sheetId="3" r:id="rId3"/>
+    <sheet name="CVCSPNoCFCorp_RecMonthly" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="32">
   <si>
     <t>Result</t>
   </si>
@@ -126,9 +126,6 @@
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
 4. Payment Plan,Monthly payments of $</t>
-  </si>
-  <si>
-    <t>Wed Dec 31 22:06:31 IST 2025</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -156,9 +153,6 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t>Thu Jan 01 19:20:55 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6207-402998,
 1. Review bill to pay,
@@ -183,12 +177,6 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t>Thu Jan 01 23:15:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 02 19:41:32 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6207-402998,
 1. Review bill to pay,
@@ -213,61 +201,72 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fri Jan 02 19:46:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:27:25 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 03 20:28:10 IST 2026</t>
   </si>
   <si>
-    <t>Fri Jul 03 20:28:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:29:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:31:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:32:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:33:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:34:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:35:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:36:52 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 03 20:38:04 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jul 06 13:39:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 15:03:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 15:10:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 15:24:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jul 21 19:12:53 IST 2026</t>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6207-402998,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,Google,_x000D_
+First Name:,Sahil,_x000D_
+Last Name:,Malhotra,_x000D_
+Routing Number:,****2691,_x000D_
+Account Number:,****8901,_x000D_
+Billing Address:,	33 Sonoma Street,_x000D_
+Manhattan,  New York ,  10008,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Monthly,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 18:58:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 19:06:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6207-402998,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,Sahil,_x000D_
+Last Name:,Malhotra,_x000D_
+Routing Number:,****2691,_x000D_
+Account Number:,****8902,_x000D_
+Billing Address:,	33 Sonoma Street,_x000D_
+Manhattan,  New York ,  10008,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Monthly,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 19:10:02 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -336,46 +335,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="164" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="2" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -392,10 +391,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -430,7 +429,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -465,7 +464,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -559,21 +558,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -590,7 +589,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -642,14 +641,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -657,7 +656,7 @@
     <col min="11" max="11" customWidth="true" width="23.54296875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,12 +706,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -738,11 +737,11 @@
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/03/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -773,7 +772,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/03/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -781,13 +780,13 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -795,7 +794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CD28ED-6B88-4076-A023-4B2AA175CC49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CD28ED-6B88-4076-A023-4B2AA175CC49}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -804,7 +803,7 @@
     <col min="15" max="15" customWidth="true" width="23.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,12 +853,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -889,7 +888,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/03/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -920,7 +919,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/03/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -928,25 +927,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38E6C38-F14D-4B06-9F0D-017FEF3E0BF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38E6C38-F14D-4B06-9F0D-017FEF3E0BF1}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="32.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,12 +995,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1027,11 +1026,11 @@
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/03/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1039,56 +1038,32 @@
       <c r="N2" s="8">
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6207-402998,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,Sahil,
-Last Name:,Malhotra,
-Routing Number:,****2691,
-Account Number:,****5489,
-Billing Address:,	33 Sonoma Street,
-Manhattan,  New York ,  10008,
-Country:,	UNITED STATES,
-Account Type:,Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Monthly,
-Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/03/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACB12DE-9459-4B21-A76D-74D1C2CFA77A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACB12DE-9459-4B21-A76D-74D1C2CFA77A}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,12 +1113,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1169,11 +1144,11 @@
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/03/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1181,44 +1156,19 @@
       <c r="N2" s="8">
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6207-402998,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,Google,
-First Name:,Sahil,
-Last Name:,Malhotra,
-Routing Number:,****2691,
-Account Number:,****5489,
-Billing Address:,	33 Sonoma Street,
-Manhattan,  New York ,  10008,
-Country:,	UNITED STATES,
-Account Type:,Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Monthly,
-Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/03/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 01/03/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>